--- a/testing_papa_pizza.xlsx
+++ b/testing_papa_pizza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zohir\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B07DE0-B385-4AD7-B1B7-782A721039CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81C8B34-F7A6-4AD0-B580-2DD160EEA79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="2160" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{96D55790-46A4-46A3-8E66-505D356AE36B}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{96D55790-46A4-46A3-8E66-505D356AE36B}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>Номер</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Подвал</t>
-  </si>
-  <si>
-    <t>Корзина</t>
   </si>
   <si>
     <t>Изображение "PAPA PIZZA"</t>
@@ -87,9 +84,6 @@
 "PAPA PIZZA"</t>
   </si>
   <si>
-    <t>1. Найдите в шапке сайта кнопку "Пицца"</t>
-  </si>
-  <si>
     <t>2. Кликнуть на кнопку "Пицца"</t>
   </si>
   <si>
@@ -106,13 +100,133 @@
     <t>Пройден</t>
   </si>
   <si>
-    <t>Кнопку "Пицца"</t>
-  </si>
-  <si>
-    <t>Пользователь успешно переходит во вкладку "Пицца"</t>
-  </si>
-  <si>
-    <t>Товар</t>
+    <t>4. Кликнуть на кнопку "Напитки"</t>
+  </si>
+  <si>
+    <t>6. Кликнуть на кнопку "Горячие закуски"</t>
+  </si>
+  <si>
+    <t>8. Кликнуть на кнопку "Комбо"</t>
+  </si>
+  <si>
+    <t>10. Кликнуть на кнопку "Соусы к пицце"</t>
+  </si>
+  <si>
+    <t>Навигационное меню</t>
+  </si>
+  <si>
+    <t>1. Найдите в навигационом меню сайта кнопку "Пицца"</t>
+  </si>
+  <si>
+    <t>Пользователь успешно переходит по навигационому меню</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шапка </t>
+  </si>
+  <si>
+    <t>5. Найдите в навигационом меню сайта кнопку "Горячие закуски"</t>
+  </si>
+  <si>
+    <t>3. Найдите в навигационом меню сайта кнопку "Напитки"</t>
+  </si>
+  <si>
+    <t>7. Найдите в навигационом меню сайта кнопку "Комбо"</t>
+  </si>
+  <si>
+    <t>9. Найдите в навигационом меню сайта кнопку "Соусы к пицце"</t>
+  </si>
+  <si>
+    <t>1. Найдите в шапке сайта кнопку "Акции"</t>
+  </si>
+  <si>
+    <t>2. Кликнуть на кнопку "Акции"</t>
+  </si>
+  <si>
+    <t>3. Найдите в шапке сайта кнопку "Условия доставки"</t>
+  </si>
+  <si>
+    <t>4. Кликнуть на кнопку "Условия доставки"</t>
+  </si>
+  <si>
+    <t>5. Найдите в шапке сайта кнопку "Оплата"</t>
+  </si>
+  <si>
+    <t>6. Кликнуть на кнопку "Оплата"</t>
+  </si>
+  <si>
+    <t>Пользователь успешно 
+проходит по кнопка в шапке</t>
+  </si>
+  <si>
+    <t>Карточка товара</t>
+  </si>
+  <si>
+    <t>1. В списке пицц найти «Супермясная»</t>
+  </si>
+  <si>
+    <t>2. Кликнуть на карточку товара "Супермясная"</t>
+  </si>
+  <si>
+    <t>3. Найдите в блоке выбора размера пиццы кнопку "L (38 см)"</t>
+  </si>
+  <si>
+    <t>4. Кликнуть на кнопку "L (38 см)"</t>
+  </si>
+  <si>
+    <t>5. Найдите снизу кнопку "В корзину"</t>
+  </si>
+  <si>
+    <t>6. Кликнуть на кнопку "В корзину"</t>
+  </si>
+  <si>
+    <t>Пользователь успешно 
+добавляет товар в корзину</t>
+  </si>
+  <si>
+    <t>1. Спуститься вниз до подвала и найти кнопку "Пиццерия"</t>
+  </si>
+  <si>
+    <t>2. Кликнуть на кнопку "Пиццерия"</t>
+  </si>
+  <si>
+    <t>4. Кликнуть на кнопку "Условия бесплатной доставки"</t>
+  </si>
+  <si>
+    <t>3. Найдите внизу подвала кнопку "Условия бесплатной доставки"</t>
+  </si>
+  <si>
+    <t>5. Спуститься вниз до подвала и найти кнопку "Оплата"</t>
+  </si>
+  <si>
+    <t>7. Найдите внизу подвала кнопку "Политика конфиденциальности"</t>
+  </si>
+  <si>
+    <t>8. Кликнуть на кнопку "Политика конфиденциальности"</t>
+  </si>
+  <si>
+    <t>9. Спуститься вниз до подвала и найти кнопку "Публичная оферта"</t>
+  </si>
+  <si>
+    <t>10. Кликнуть на кнопку "Публичная оферта"</t>
+  </si>
+  <si>
+    <t>Пользователь успешно 
+проходит по кнопка в подвале</t>
+  </si>
+  <si>
+    <t>1. Найдите в навигационом меню сайта кнопку "Комбо"</t>
+  </si>
+  <si>
+    <t>2. Кликнуть на кнопку "Комбо"</t>
+  </si>
+  <si>
+    <t>3. Найдите ползунок "Цена"</t>
+  </si>
+  <si>
+    <t>4. Переместить правый ползунок на значение «3 064 р.»</t>
+  </si>
+  <si>
+    <t>Пользователь успешно передвигает ползунок и у него остается 2 товара</t>
   </si>
 </sst>
 </file>
@@ -261,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -285,16 +399,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -306,6 +417,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -675,7 +793,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -683,7 +801,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -691,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -699,7 +817,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -740,12 +858,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B16BA205-338B-4563-A024-A0FE4996EEF1}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="48.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="61.85546875" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
@@ -753,125 +871,517 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15"/>
+        <v>6</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="15"/>
+      <c r="F3" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="8" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>20</v>
+      <c r="B7" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="9"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="11"/>
+        <v>13</v>
+      </c>
+      <c r="D8" s="10"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>3</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>4</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>5</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>6</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
+  <mergeCells count="31">
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="A29:A38"/>
+    <mergeCell ref="B29:B38"/>
+    <mergeCell ref="F29:F38"/>
+    <mergeCell ref="E29:E38"/>
+    <mergeCell ref="D29:D38"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="F23:F28"/>
+    <mergeCell ref="E23:E28"/>
+    <mergeCell ref="D23:D28"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="F17:F22"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="E3:E6"/>
     <mergeCell ref="F3:F6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A16"/>
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="D7:D16"/>
+    <mergeCell ref="F7:F16"/>
+    <mergeCell ref="E7:E16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
